--- a/ru/downloads/data-excel/9.1.2.xlsx
+++ b/ru/downloads/data-excel/9.1.2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -523,7 +523,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -649,6 +649,18 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="19" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="19" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="21">
@@ -974,14 +986,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="35.85546875" customWidth="1"/>
     <col min="9" max="9" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="1" customFormat="1" ht="42.75" customHeight="1">
+    <row r="1" spans="1:21" s="1" customFormat="1" ht="42.75" customHeight="1">
       <c r="A1" s="21" t="s">
         <v>38</v>
       </c>
@@ -998,7 +1010,7 @@
       <c r="H1" s="22"/>
       <c r="I1" s="11"/>
     </row>
-    <row r="2" spans="1:20" ht="15.75" thickBot="1">
+    <row r="2" spans="1:21" ht="15.75" thickBot="1">
       <c r="A2" s="22"/>
       <c r="B2" s="23"/>
       <c r="C2" s="22"/>
@@ -1008,8 +1020,9 @@
       <c r="G2" s="22"/>
       <c r="H2" s="22"/>
       <c r="I2" s="22"/>
-    </row>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1">
+      <c r="U2" s="1"/>
+    </row>
+    <row r="3" spans="1:21" ht="15.75" thickBot="1">
       <c r="A3" s="24" t="s">
         <v>20</v>
       </c>
@@ -1070,8 +1083,11 @@
       <c r="T3" s="26">
         <v>2023</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" ht="41.25" customHeight="1">
+      <c r="U3" s="26">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="41.25" customHeight="1">
       <c r="A4" s="43" t="s">
         <v>41</v>
       </c>
@@ -1132,8 +1148,11 @@
       <c r="T4" s="33">
         <v>11350.7</v>
       </c>
-    </row>
-    <row r="5" spans="1:20">
+      <c r="U4" s="44">
+        <v>11802.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5" s="28" t="s">
         <v>23</v>
       </c>
@@ -1194,8 +1213,11 @@
       <c r="T5" s="35">
         <v>21.6</v>
       </c>
-    </row>
-    <row r="6" spans="1:20">
+      <c r="U5" s="45">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6" s="28" t="s">
         <v>26</v>
       </c>
@@ -1256,8 +1278,11 @@
       <c r="T6" s="35">
         <v>7996.3</v>
       </c>
-    </row>
-    <row r="7" spans="1:20">
+      <c r="U6" s="45">
+        <v>8495.7999999999993</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" s="28" t="s">
         <v>29</v>
       </c>
@@ -1318,8 +1343,11 @@
       <c r="T7" s="35">
         <v>145.4</v>
       </c>
-    </row>
-    <row r="8" spans="1:20">
+      <c r="U7" s="45">
+        <v>82.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8" s="28" t="s">
         <v>32</v>
       </c>
@@ -1380,8 +1408,11 @@
       <c r="T8" s="35">
         <v>1060.7</v>
       </c>
-    </row>
-    <row r="9" spans="1:20">
+      <c r="U8" s="45">
+        <v>1223.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9" s="28" t="s">
         <v>34</v>
       </c>
@@ -1440,8 +1471,11 @@
       <c r="T9" s="35">
         <v>2126.6999999999998</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" s="1" customFormat="1" ht="37.5" customHeight="1">
+      <c r="U9" s="45">
+        <v>1975.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" s="1" customFormat="1" ht="37.5" customHeight="1">
       <c r="A10" s="29" t="s">
         <v>43</v>
       </c>
@@ -1502,8 +1536,11 @@
       <c r="T10" s="36">
         <v>2985.3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" s="1" customFormat="1">
+      <c r="U10" s="46">
+        <v>3180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" s="1" customFormat="1">
       <c r="A11" s="16" t="s">
         <v>47</v>
       </c>
@@ -1564,8 +1601,11 @@
       <c r="T11" s="38">
         <v>1085.5999999999999</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" s="1" customFormat="1">
+      <c r="U11" s="47">
+        <v>1075.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" s="1" customFormat="1">
       <c r="A12" s="16" t="s">
         <v>19</v>
       </c>
@@ -1626,8 +1666,11 @@
       <c r="T12" s="38">
         <v>1403.6</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" s="1" customFormat="1">
+      <c r="U12" s="47">
+        <v>1531.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" s="1" customFormat="1">
       <c r="A13" s="16" t="s">
         <v>21</v>
       </c>
@@ -1688,8 +1731,11 @@
       <c r="T13" s="38">
         <v>265</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" s="1" customFormat="1">
+      <c r="U13" s="47">
+        <v>320.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" s="1" customFormat="1">
       <c r="A14" s="17" t="s">
         <v>8</v>
       </c>
@@ -1750,8 +1796,9 @@
       <c r="T14" s="40" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" s="1" customFormat="1" ht="15.75" thickBot="1">
+      <c r="U14" s="47"/>
+    </row>
+    <row r="15" spans="1:21" s="1" customFormat="1" ht="15.75" thickBot="1">
       <c r="A15" s="18" t="s">
         <v>9</v>
       </c>
@@ -1812,8 +1859,11 @@
       <c r="T15" s="42">
         <v>231.1</v>
       </c>
-    </row>
-    <row r="16" spans="1:20">
+      <c r="U15" s="42">
+        <v>252.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16" s="15" t="s">
         <v>3</v>
       </c>
